--- a/monitor_xlsx/20260305.xlsx
+++ b/monitor_xlsx/20260305.xlsx
@@ -544,10 +544,6 @@
           <t>+1.72%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-0.54%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>-0.33%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>-1.17%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>+12.29%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -669,7 +649,6 @@
           <t>-514.95億</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>-584.74億</t>
@@ -707,7 +686,6 @@
           <t>144.67億</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>64.83億</t>
@@ -718,8 +696,6 @@
           <t>324.17億</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -737,15 +713,11 @@
           <t>128.98%</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>134.73%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -763,11 +735,6 @@
           <t>-458.02億</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -785,15 +752,11 @@
           <t>11679口</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>16801口</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -811,7 +774,6 @@
           <t>-31.18億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>2.79億</t>
@@ -916,10 +878,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1041,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1076,6 +1034,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1267,7 +1226,6 @@
           <t>S&amp;P黃金正2</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="G5" s="6" t="n">
         <v>-54</v>
       </c>
@@ -2124,46 +2082,46 @@
           <t>智邦</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
+      <c r="C19" t="n">
         <v>1420</v>
       </c>
+      <c r="D19" s="6" t="n">
+        <v>8.81</v>
+      </c>
       <c r="E19" s="6" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="F19" t="n">
         <v>4477</v>
       </c>
+      <c r="F19" s="7" t="n">
+        <v>597</v>
+      </c>
       <c r="G19" s="7" t="n">
-        <v>597</v>
+        <v>-173</v>
       </c>
       <c r="H19" t="n">
-        <v>-754</v>
+        <v>-62</v>
       </c>
       <c r="I19" t="n">
-        <v>-62</v>
+        <v>-439</v>
       </c>
       <c r="J19" t="n">
-        <v>-373</v>
+        <v>65</v>
       </c>
       <c r="K19" t="n">
-        <v>65</v>
+        <v>1815</v>
       </c>
       <c r="L19" t="n">
-        <v>1815</v>
+        <v>9488</v>
       </c>
       <c r="M19" t="n">
-        <v>9453</v>
+        <v>-140164</v>
       </c>
       <c r="N19" t="n">
-        <v>-140164</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.57</v>
+        <v>10.1</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>主力積極賣出</t>
+        </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -2233,6 +2191,59 @@
       <c r="W20" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3894</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>317</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3065</v>
+      </c>
+      <c r="H21" t="n">
+        <v>304</v>
+      </c>
+      <c r="I21" t="n">
+        <v>965</v>
+      </c>
+      <c r="J21" t="n">
+        <v>121</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2151</v>
+      </c>
+      <c r="L21" t="n">
+        <v>10988</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-47552</v>
+      </c>
+      <c r="N21" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>偏多</t>
         </is>
       </c>
     </row>

--- a/monitor_xlsx/20260305.xlsx
+++ b/monitor_xlsx/20260305.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2247,165 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>962</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>826</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>276</v>
+      </c>
+      <c r="G22" t="n">
+        <v>315</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-25</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-19</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-98</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>624</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>343</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5076</v>
+      </c>
+      <c r="H23" t="n">
+        <v>119</v>
+      </c>
+      <c r="I23" t="n">
+        <v>330</v>
+      </c>
+      <c r="J23" t="n">
+        <v>43</v>
+      </c>
+      <c r="K23" t="n">
+        <v>16</v>
+      </c>
+      <c r="L23" t="n">
+        <v>346</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1405</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2835</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-3461</v>
+      </c>
+      <c r="H24" t="n">
+        <v>142</v>
+      </c>
+      <c r="I24" t="n">
+        <v>104</v>
+      </c>
+      <c r="J24" t="n">
+        <v>172</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3031</v>
+      </c>
+      <c r="L24" t="n">
+        <v>11922</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-106279</v>
+      </c>
+      <c r="N24" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/monitor_xlsx/20260305.xlsx
+++ b/monitor_xlsx/20260305.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2406,6 +2406,59 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>德律</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>249</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="E25" t="n">
+        <v>10769</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-467</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2683</v>
+      </c>
+      <c r="H25" t="n">
+        <v>121</v>
+      </c>
+      <c r="I25" t="n">
+        <v>480</v>
+      </c>
+      <c r="J25" t="n">
+        <v>383</v>
+      </c>
+      <c r="K25" t="n">
+        <v>7193</v>
+      </c>
+      <c r="L25" t="n">
+        <v>35567</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-58840</v>
+      </c>
+      <c r="N25" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
